--- a/gcc_data.xlsx
+++ b/gcc_data.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasimalhamrani/Desktop/gcc-macro-model/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF53E85-2B65-7B49-B05B-97872AB0939A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="600" windowWidth="25600" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="gcc_data_formatted" sheetId="1" r:id="rId5"/>
+    <sheet name="gcc_data_formatted" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -43,20 +52,22 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -65,43 +76,44 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -291,17 +303,20 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -330,15 +345,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2">
-        <v>43646.0</v>
+        <v>43646</v>
       </c>
       <c r="B2" s="1">
         <v>68.3</v>
       </c>
       <c r="C2" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D2" s="1">
         <v>1.5</v>
@@ -359,24 +374,24 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2">
-        <v>43738.0</v>
+        <v>43738</v>
       </c>
       <c r="B3" s="1">
-        <v>62.0</v>
+        <v>62</v>
       </c>
       <c r="C3" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D3" s="1">
         <v>0.85</v>
       </c>
       <c r="E3" s="1">
-        <v>-4.6</v>
+        <v>-4.5999999999999996</v>
       </c>
       <c r="F3" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G3" s="1">
         <v>1.66</v>
@@ -388,73 +403,73 @@
         <v>1.57</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2">
-        <v>43830.0</v>
+        <v>43830</v>
       </c>
       <c r="B4" s="1">
         <v>63.2</v>
       </c>
       <c r="C4" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D4" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="E4" s="1">
-        <v>-10.0</v>
+        <v>-10</v>
       </c>
       <c r="F4" s="1">
         <v>-4.63</v>
       </c>
       <c r="G4" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="H4" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="I4" s="1">
-        <v>-10.0</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2">
-        <v>43921.0</v>
+        <v>43921</v>
       </c>
       <c r="B5" s="1">
         <v>50.4</v>
       </c>
       <c r="C5" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D5" s="1">
-        <v>-10.0</v>
+        <v>-10</v>
       </c>
       <c r="E5" s="1">
         <v>2.06</v>
       </c>
       <c r="F5" s="1">
-        <v>-8.62</v>
+        <v>-8.6199999999999992</v>
       </c>
       <c r="G5" s="1">
-        <v>-10.0</v>
+        <v>-10</v>
       </c>
       <c r="H5" s="1">
-        <v>-10.0</v>
+        <v>-10</v>
       </c>
       <c r="I5" s="1">
         <v>-9.76</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2">
-        <v>44012.0</v>
+        <v>44012</v>
       </c>
       <c r="B6" s="1">
         <v>29.3</v>
       </c>
       <c r="C6" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D6" s="1">
         <v>-7.32</v>
@@ -466,7 +481,7 @@
         <v>-5.8</v>
       </c>
       <c r="G6" s="1">
-        <v>-10.2</v>
+        <v>-10.199999999999999</v>
       </c>
       <c r="H6" s="1">
         <v>-7.61</v>
@@ -475,15 +490,15 @@
         <v>-10.79</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2">
-        <v>44104.0</v>
+        <v>44104</v>
       </c>
       <c r="B7" s="1">
         <v>42.9</v>
       </c>
       <c r="C7" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D7" s="1">
         <v>-3.69</v>
@@ -495,7 +510,7 @@
         <v>-4.38</v>
       </c>
       <c r="G7" s="1">
-        <v>-8.37</v>
+        <v>-8.3699999999999992</v>
       </c>
       <c r="H7" s="1">
         <v>-4.32</v>
@@ -504,15 +519,15 @@
         <v>-6.96</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2">
-        <v>44196.0</v>
+        <v>44196</v>
       </c>
       <c r="B8" s="1">
         <v>44.2</v>
       </c>
       <c r="C8" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D8" s="1">
         <v>-2.94</v>
@@ -533,15 +548,15 @@
         <v>-4.22</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2">
-        <v>44286.0</v>
+        <v>44286</v>
       </c>
       <c r="B9" s="1">
         <v>61.1</v>
       </c>
       <c r="C9" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D9" s="1">
         <v>1.72</v>
@@ -550,10 +565,10 @@
         <v>-4.12</v>
       </c>
       <c r="F9" s="1">
-        <v>-2.07</v>
+        <v>-2.0699999999999998</v>
       </c>
       <c r="G9" s="1">
-        <v>-8.38</v>
+        <v>-8.3800000000000008</v>
       </c>
       <c r="H9" s="1">
         <v>-1.4</v>
@@ -562,15 +577,15 @@
         <v>-2.09</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2">
-        <v>44377.0</v>
+        <v>44377</v>
       </c>
       <c r="B10" s="1">
-        <v>68.9</v>
+        <v>68.900000000000006</v>
       </c>
       <c r="C10" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D10" s="1">
         <v>6.89</v>
@@ -582,7 +597,7 @@
         <v>4.16</v>
       </c>
       <c r="G10" s="1">
-        <v>8.71</v>
+        <v>8.7100000000000009</v>
       </c>
       <c r="H10" s="1">
         <v>5.15</v>
@@ -591,18 +606,18 @@
         <v>7.78</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2">
-        <v>44469.0</v>
+        <v>44469</v>
       </c>
       <c r="B11" s="1">
-        <v>73.4</v>
+        <v>73.400000000000006</v>
       </c>
       <c r="C11" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D11" s="1">
-        <v>8.53</v>
+        <v>8.5299999999999994</v>
       </c>
       <c r="E11" s="1">
         <v>7.58</v>
@@ -617,27 +632,27 @@
         <v>4.17</v>
       </c>
       <c r="I11" s="1">
-        <v>4.06</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>4.0599999999999996</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2">
-        <v>44561.0</v>
+        <v>44561</v>
       </c>
       <c r="B12" s="1">
         <v>79.7</v>
       </c>
       <c r="C12" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D12" s="1">
         <v>8.98</v>
       </c>
       <c r="E12" s="1">
-        <v>9.03</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="F12" s="1">
-        <v>2.22</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="G12" s="1">
         <v>5.64</v>
@@ -649,15 +664,15 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2">
-        <v>44651.0</v>
+        <v>44651</v>
       </c>
       <c r="B13" s="1">
         <v>97.9</v>
       </c>
       <c r="C13" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D13" s="1">
         <v>11.17</v>
@@ -678,15 +693,15 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2">
-        <v>44742.0</v>
+        <v>44742</v>
       </c>
       <c r="B14" s="1">
         <v>113.9</v>
       </c>
       <c r="C14" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D14" s="1">
         <v>14.49</v>
@@ -707,15 +722,15 @@
         <v>8.51</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2">
-        <v>44834.0</v>
+        <v>44834</v>
       </c>
       <c r="B15" s="1">
         <v>97.7</v>
       </c>
       <c r="C15" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D15" s="1">
         <v>12.98</v>
@@ -727,7 +742,7 @@
         <v>4.42</v>
       </c>
       <c r="G15" s="1">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="H15" s="1">
         <v>9.17</v>
@@ -736,15 +751,15 @@
         <v>4.38</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="2">
-        <v>44926.0</v>
+        <v>44926</v>
       </c>
       <c r="B16" s="1">
         <v>88.5</v>
       </c>
       <c r="C16" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D16" s="1">
         <v>9.61</v>
@@ -765,21 +780,21 @@
         <v>4.84</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="2">
-        <v>45016.0</v>
+        <v>45016</v>
       </c>
       <c r="B17" s="1">
         <v>81.2</v>
       </c>
       <c r="C17" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D17" s="1">
         <v>5.52</v>
       </c>
       <c r="E17" s="1">
-        <v>4.81</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="F17" s="1">
         <v>4.8</v>
@@ -791,18 +806,18 @@
         <v>3.4</v>
       </c>
       <c r="I17" s="1">
-        <v>2.24</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>2.2400000000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="2">
-        <v>45107.0</v>
+        <v>45107</v>
       </c>
       <c r="B18" s="1">
-        <v>78.0</v>
+        <v>78</v>
       </c>
       <c r="C18" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D18" s="1">
         <v>2.68</v>
@@ -811,7 +826,7 @@
         <v>4.53</v>
       </c>
       <c r="F18" s="1">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="G18" s="1">
         <v>-1.98</v>
@@ -823,15 +838,15 @@
         <v>2.23</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="2">
-        <v>45199.0</v>
+        <v>45199</v>
       </c>
       <c r="B19" s="1">
         <v>86.7</v>
       </c>
       <c r="C19" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D19" s="1">
         <v>-2.64</v>
@@ -852,21 +867,21 @@
         <v>4.04</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="2">
-        <v>45291.0</v>
+        <v>45291</v>
       </c>
       <c r="B20" s="1">
         <v>82.7</v>
       </c>
       <c r="C20" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D20" s="1">
         <v>-2.96</v>
       </c>
       <c r="E20" s="1">
-        <v>4.69</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="F20" s="1">
         <v>-3.57</v>
@@ -881,15 +896,15 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2">
-        <v>45382.0</v>
+        <v>45382</v>
       </c>
       <c r="B21" s="1">
         <v>83.5</v>
       </c>
       <c r="C21" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D21" s="1">
         <v>0.37</v>
@@ -910,15 +925,15 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="2">
-        <v>45473.0</v>
+        <v>45473</v>
       </c>
       <c r="B22" s="1">
-        <v>85.0</v>
+        <v>85</v>
       </c>
       <c r="C22" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D22" s="1">
         <v>1.18</v>
@@ -930,30 +945,30 @@
         <v>1.49</v>
       </c>
       <c r="G22" s="1">
-        <v>-1.13</v>
+        <v>-1.1299999999999999</v>
       </c>
       <c r="H22" s="1">
-        <v>2.07</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="I22" s="1">
         <v>1.17</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="2">
-        <v>45565.0</v>
+        <v>45565</v>
       </c>
       <c r="B23" s="1">
         <v>78.5</v>
       </c>
       <c r="C23" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D23" s="1">
         <v>3.91</v>
       </c>
       <c r="E23" s="1">
-        <v>4.27</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="F23" s="1">
         <v>2.35</v>
@@ -968,15 +983,15 @@
         <v>3.14</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="2">
-        <v>45657.0</v>
+        <v>45657</v>
       </c>
       <c r="B24" s="1">
-        <v>75.0</v>
+        <v>75</v>
       </c>
       <c r="C24" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D24" s="1">
         <v>5.17</v>
@@ -997,15 +1012,15 @@
         <v>3.95</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="2">
-        <v>45747.0</v>
+        <v>45747</v>
       </c>
       <c r="B25" s="1">
-        <v>76.0</v>
+        <v>76</v>
       </c>
       <c r="C25" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D25" s="1">
         <v>3.68</v>
@@ -1026,21 +1041,21 @@
         <v>2.88</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="2">
-        <v>45838.0</v>
+        <v>45838</v>
       </c>
       <c r="B26" s="1">
-        <v>71.0</v>
+        <v>71</v>
       </c>
       <c r="C26" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D26" s="1">
         <v>4.46</v>
       </c>
       <c r="E26" s="1">
-        <v>4.52</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="F26" s="1">
         <v>1.87</v>
@@ -1055,15 +1070,15 @@
         <v>2.74</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="2">
-        <v>45930.0</v>
+        <v>45930</v>
       </c>
       <c r="B27" s="1">
-        <v>67.0</v>
+        <v>67</v>
       </c>
       <c r="C27" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D27" s="1">
         <v>4.82</v>
@@ -1078,27 +1093,30 @@
         <v>4.8</v>
       </c>
       <c r="H27" s="1">
-        <v>2.45</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="I27" s="1">
         <v>4.03</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="2">
-        <v>46022.0</v>
+        <v>46022</v>
       </c>
       <c r="B28" s="1">
-        <v>62.0</v>
+        <v>62</v>
       </c>
       <c r="C28" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D28" s="1">
         <v>5.03</v>
       </c>
+      <c r="E28" s="1">
+        <v>4.5</v>
+      </c>
       <c r="F28" s="1">
-        <v>2.03</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="G28" s="1">
         <v>2.82</v>
@@ -1107,10 +1125,10 @@
         <v>2.17</v>
       </c>
       <c r="I28" s="1">
-        <v>4.56</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>